--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/184.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/184.xlsx
@@ -426,13 +426,13 @@
         <v>6.887317467148282</v>
       </c>
       <c r="E2">
-        <v>-14.13882626582603</v>
+        <v>-10.99583888080242</v>
       </c>
       <c r="F2">
-        <v>-3.429065944403993</v>
+        <v>-3.399684580994097</v>
       </c>
       <c r="G2">
-        <v>-7.498141816747666</v>
+        <v>-5.508335109823181</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>6.666311507021283</v>
       </c>
       <c r="E3">
-        <v>-13.19645082482983</v>
+        <v>-11.29492647511302</v>
       </c>
       <c r="F3">
-        <v>-3.733234999405346</v>
+        <v>-3.587660197139569</v>
       </c>
       <c r="G3">
-        <v>-7.28813073937292</v>
+        <v>-5.979866042618193</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>6.35503361786376</v>
       </c>
       <c r="E4">
-        <v>-13.23229822507455</v>
+        <v>-11.43524577071469</v>
       </c>
       <c r="F4">
-        <v>-3.687350900596879</v>
+        <v>-3.549003603920528</v>
       </c>
       <c r="G4">
-        <v>-7.036827227486844</v>
+        <v>-4.768951247991275</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>5.987149104723374</v>
       </c>
       <c r="E5">
-        <v>-15.44701636563585</v>
+        <v>-12.49030323044375</v>
       </c>
       <c r="F5">
-        <v>-3.808247809565855</v>
+        <v>-3.23633798446866</v>
       </c>
       <c r="G5">
-        <v>-6.708838238729091</v>
+        <v>-4.496023252642679</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>5.583540838237232</v>
       </c>
       <c r="E6">
-        <v>-14.16346569290176</v>
+        <v>-12.85742661824559</v>
       </c>
       <c r="F6">
-        <v>-4.002072527942495</v>
+        <v>-3.285933169241669</v>
       </c>
       <c r="G6">
-        <v>-6.488001677440928</v>
+        <v>-4.830196340467792</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>5.17717910283086</v>
       </c>
       <c r="E7">
-        <v>-15.01226021852946</v>
+        <v>-13.80224290673192</v>
       </c>
       <c r="F7">
-        <v>-4.358118091544167</v>
+        <v>-3.15286837149297</v>
       </c>
       <c r="G7">
-        <v>-6.338825184895828</v>
+        <v>-3.984246017726747</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.792813239251656</v>
       </c>
       <c r="E8">
-        <v>-16.26369042512714</v>
+        <v>-13.25709162026654</v>
       </c>
       <c r="F8">
-        <v>-3.916320762772093</v>
+        <v>-3.732371840571629</v>
       </c>
       <c r="G8">
-        <v>-6.208733987384628</v>
+        <v>-4.245547377141421</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.456225702567931</v>
       </c>
       <c r="E9">
-        <v>-15.87786896814763</v>
+        <v>-14.06123992065261</v>
       </c>
       <c r="F9">
-        <v>-4.260784921715225</v>
+        <v>-3.537664082543605</v>
       </c>
       <c r="G9">
-        <v>-7.294506850081556</v>
+        <v>-3.665907269215969</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.191827299520505</v>
       </c>
       <c r="E10">
-        <v>-15.8281417950694</v>
+        <v>-15.2196869704508</v>
       </c>
       <c r="F10">
-        <v>-4.385889108723021</v>
+        <v>-3.980780172220936</v>
       </c>
       <c r="G10">
-        <v>-5.956798161300552</v>
+        <v>-3.522712932460333</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>4.012360957149699</v>
       </c>
       <c r="E11">
-        <v>-16.8425426151576</v>
+        <v>-14.62732634245545</v>
       </c>
       <c r="F11">
-        <v>-4.269272374124309</v>
+        <v>-3.46533021256375</v>
       </c>
       <c r="G11">
-        <v>-4.895010201035643</v>
+        <v>-3.460981189789543</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>3.925614134451256</v>
       </c>
       <c r="E12">
-        <v>-16.95900138121286</v>
+        <v>-15.7606584754071</v>
       </c>
       <c r="F12">
-        <v>-3.806413804136057</v>
+        <v>-3.826056880358642</v>
       </c>
       <c r="G12">
-        <v>-5.201917635799318</v>
+        <v>-2.982743091731967</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.927317393898028</v>
       </c>
       <c r="E13">
-        <v>-18.42533032184454</v>
+        <v>-16.40141490512242</v>
       </c>
       <c r="F13">
-        <v>-4.026491970609621</v>
+        <v>-3.52185551902858</v>
       </c>
       <c r="G13">
-        <v>-3.892428037195061</v>
+        <v>-2.644461616892619</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>4.012364128124159</v>
       </c>
       <c r="E14">
-        <v>-19.4235916605694</v>
+        <v>-16.43249835071107</v>
       </c>
       <c r="F14">
-        <v>-4.397648612373162</v>
+        <v>-3.32689759404491</v>
       </c>
       <c r="G14">
-        <v>-4.635211829295797</v>
+        <v>-3.010743685903122</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.161702031365782</v>
       </c>
       <c r="E15">
-        <v>-20.07765727539326</v>
+        <v>-16.94749905723338</v>
       </c>
       <c r="F15">
-        <v>-4.382358606852289</v>
+        <v>-3.805540704893506</v>
       </c>
       <c r="G15">
-        <v>-4.825886010175661</v>
+        <v>-1.640237422464558</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.35508736379459</v>
       </c>
       <c r="E16">
-        <v>-20.31819622925869</v>
+        <v>-18.20654615711196</v>
       </c>
       <c r="F16">
-        <v>-3.965777610188835</v>
+        <v>-3.146685437198475</v>
       </c>
       <c r="G16">
-        <v>-3.90006215520862</v>
+        <v>-0.8712639046026464</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.571065859725785</v>
       </c>
       <c r="E17">
-        <v>-20.69881446960338</v>
+        <v>-18.69715197415495</v>
       </c>
       <c r="F17">
-        <v>-4.023089865686324</v>
+        <v>-3.587030637913442</v>
       </c>
       <c r="G17">
-        <v>-2.734283338464125</v>
+        <v>-0.756775308218031</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.78639164524067</v>
       </c>
       <c r="E18">
-        <v>-21.15120449449564</v>
+        <v>-20.67654343443366</v>
       </c>
       <c r="F18">
-        <v>-3.680015707245089</v>
+        <v>-3.292280948649322</v>
       </c>
       <c r="G18">
-        <v>-1.568852129001253</v>
+        <v>-0.7689316314382347</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.97941683807657</v>
       </c>
       <c r="E19">
-        <v>-22.23562005121643</v>
+        <v>-19.14070241778424</v>
       </c>
       <c r="F19">
-        <v>-3.832237329550929</v>
+        <v>-3.044032491908755</v>
       </c>
       <c r="G19">
-        <v>-2.694599829084881</v>
+        <v>-0.5153537747666797</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.130351598441652</v>
       </c>
       <c r="E20">
-        <v>-23.30859668259384</v>
+        <v>-20.85952548366159</v>
       </c>
       <c r="F20">
-        <v>-3.706875520280863</v>
+        <v>-2.724418526682205</v>
       </c>
       <c r="G20">
-        <v>-2.211776625455414</v>
+        <v>-0.3825313771855803</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.22642454675316</v>
       </c>
       <c r="E21">
-        <v>-22.33886473011731</v>
+        <v>-20.93004288090903</v>
       </c>
       <c r="F21">
-        <v>-3.165486892139815</v>
+        <v>-2.748611825048367</v>
       </c>
       <c r="G21">
-        <v>-1.792496032906718</v>
+        <v>-0.6978773925288573</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.254623997136985</v>
       </c>
       <c r="E22">
-        <v>-22.6269119047972</v>
+        <v>-22.52207773151963</v>
       </c>
       <c r="F22">
-        <v>-3.097859805742667</v>
+        <v>-2.530776877501584</v>
       </c>
       <c r="G22">
-        <v>-2.038539087930892</v>
+        <v>-0.1297215670791361</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.208329593724436</v>
       </c>
       <c r="E23">
-        <v>-23.0346285336038</v>
+        <v>-21.73247036117219</v>
       </c>
       <c r="F23">
-        <v>-3.186538192947159</v>
+        <v>-2.344684140462675</v>
       </c>
       <c r="G23">
-        <v>-1.909669481723683</v>
+        <v>0.6021208720143096</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.084422529766829</v>
       </c>
       <c r="E24">
-        <v>-25.00426113239597</v>
+        <v>-21.32139360465191</v>
       </c>
       <c r="F24">
-        <v>-2.733011181751444</v>
+        <v>-2.167280977479133</v>
       </c>
       <c r="G24">
-        <v>-1.245736263277307</v>
+        <v>-0.02958087506172197</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.886881240497233</v>
       </c>
       <c r="E25">
-        <v>-24.68195605184805</v>
+        <v>-23.36993033455373</v>
       </c>
       <c r="F25">
-        <v>-3.061978243323003</v>
+        <v>-2.171498195926785</v>
       </c>
       <c r="G25">
-        <v>-1.723295699499332</v>
+        <v>0.4246094201985885</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.621249836585242</v>
       </c>
       <c r="E26">
-        <v>-26.09094998306861</v>
+        <v>-23.28372177486971</v>
       </c>
       <c r="F26">
-        <v>-2.569503881949863</v>
+        <v>-2.20960226808816</v>
       </c>
       <c r="G26">
-        <v>-1.671128122891497</v>
+        <v>-0.2919217457757279</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.295669256427922</v>
       </c>
       <c r="E27">
-        <v>-24.22290917016451</v>
+        <v>-23.01496589946249</v>
       </c>
       <c r="F27">
-        <v>-3.060922903251837</v>
+        <v>-2.038361330214043</v>
       </c>
       <c r="G27">
-        <v>-3.19303887602309</v>
+        <v>-0.02539303495454392</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.923955842027952</v>
       </c>
       <c r="E28">
-        <v>-24.37520175104247</v>
+        <v>-21.94456144132143</v>
       </c>
       <c r="F28">
-        <v>-2.898296986366835</v>
+        <v>-2.511403849052312</v>
       </c>
       <c r="G28">
-        <v>-1.977101983813097</v>
+        <v>-0.7460623828529493</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.521174552824578</v>
       </c>
       <c r="E29">
-        <v>-23.87196149151807</v>
+        <v>-22.17047795261609</v>
       </c>
       <c r="F29">
-        <v>-2.818541772825299</v>
+        <v>-2.003254291315997</v>
       </c>
       <c r="G29">
-        <v>-1.713820918165938</v>
+        <v>-0.6222877062306782</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.102819935834733</v>
       </c>
       <c r="E30">
-        <v>-25.42733834503658</v>
+        <v>-21.47108231297545</v>
       </c>
       <c r="F30">
-        <v>-2.17022748033089</v>
+        <v>-2.226334461257307</v>
       </c>
       <c r="G30">
-        <v>-2.070422952019613</v>
+        <v>-1.261454733497766</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.682394568418039</v>
       </c>
       <c r="E31">
-        <v>-24.24535681582054</v>
+        <v>-21.30252345346194</v>
       </c>
       <c r="F31">
-        <v>-2.005648273110088</v>
+        <v>-1.91401841284942</v>
       </c>
       <c r="G31">
-        <v>-3.081787993175882</v>
+        <v>-1.057783350830724</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.279376982169362</v>
       </c>
       <c r="E32">
-        <v>-24.12009016782036</v>
+        <v>-21.64034761443416</v>
       </c>
       <c r="F32">
-        <v>-2.614640793361006</v>
+        <v>-1.710553154639</v>
       </c>
       <c r="G32">
-        <v>-2.976254422474995</v>
+        <v>-0.707567359322304</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.907070010464483</v>
       </c>
       <c r="E33">
-        <v>-22.82170874271115</v>
+        <v>-21.76627994811346</v>
       </c>
       <c r="F33">
-        <v>-2.361973824893906</v>
+        <v>-1.904599047112187</v>
       </c>
       <c r="G33">
-        <v>-1.880258595152797</v>
+        <v>-1.252102442349325</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.575863908253154</v>
       </c>
       <c r="E34">
-        <v>-23.2897355883519</v>
+        <v>-20.68821331195142</v>
       </c>
       <c r="F34">
-        <v>-2.483095221429041</v>
+        <v>-1.99869247202878</v>
       </c>
       <c r="G34">
-        <v>-2.332479115817241</v>
+        <v>-1.34810826298819</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.294971768134675</v>
       </c>
       <c r="E35">
-        <v>-23.26385535939806</v>
+        <v>-20.5037051669829</v>
       </c>
       <c r="F35">
-        <v>-2.180803246962432</v>
+        <v>-1.829885277584088</v>
       </c>
       <c r="G35">
-        <v>-3.843984824318905</v>
+        <v>-0.917647958153375</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.071443134017376</v>
       </c>
       <c r="E36">
-        <v>-22.6827027045717</v>
+        <v>-19.83441482254525</v>
       </c>
       <c r="F36">
-        <v>-2.134442008529952</v>
+        <v>-1.707003600318004</v>
       </c>
       <c r="G36">
-        <v>-2.772924025998498</v>
+        <v>-1.835718515467443</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.9069470136548599</v>
       </c>
       <c r="E37">
-        <v>-22.15706914107938</v>
+        <v>-20.19599082968769</v>
       </c>
       <c r="F37">
-        <v>-1.988129959275684</v>
+        <v>-1.870440488890347</v>
       </c>
       <c r="G37">
-        <v>-3.876934684071271</v>
+        <v>-1.55464988863778</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.7995264805875163</v>
       </c>
       <c r="E38">
-        <v>-22.10682119349027</v>
+        <v>-19.32075907280322</v>
       </c>
       <c r="F38">
-        <v>-1.645711039450063</v>
+        <v>-1.44162947589196</v>
       </c>
       <c r="G38">
-        <v>-2.414646856101952</v>
+        <v>-0.8965498514315997</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.7487748149583835</v>
       </c>
       <c r="E39">
-        <v>-20.77060889652099</v>
+        <v>-18.50446540512858</v>
       </c>
       <c r="F39">
-        <v>-2.189824996346321</v>
+        <v>-1.232272040345427</v>
       </c>
       <c r="G39">
-        <v>-3.497536233634175</v>
+        <v>-0.8370990746373678</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.7485994230195584</v>
       </c>
       <c r="E40">
-        <v>-20.8242215002978</v>
+        <v>-19.14945142956706</v>
       </c>
       <c r="F40">
-        <v>-2.529299898422392</v>
+        <v>-1.740887140562115</v>
       </c>
       <c r="G40">
-        <v>-3.104243423568759</v>
+        <v>-1.382650495144945</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.7913071296972588</v>
       </c>
       <c r="E41">
-        <v>-18.74436584415892</v>
+        <v>-17.50380850365366</v>
       </c>
       <c r="F41">
-        <v>-1.8548033974277</v>
+        <v>-1.53997988089154</v>
       </c>
       <c r="G41">
-        <v>-2.989850833004782</v>
+        <v>-1.297039787499392</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.8667958393826269</v>
       </c>
       <c r="E42">
-        <v>-21.03161202442707</v>
+        <v>-16.32491086523683</v>
       </c>
       <c r="F42">
-        <v>-2.771409324340812</v>
+        <v>-1.573488170702183</v>
       </c>
       <c r="G42">
-        <v>-3.010833070632683</v>
+        <v>-1.714615449095364</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.9656157918007056</v>
       </c>
       <c r="E43">
-        <v>-19.16237116591094</v>
+        <v>-16.69193915508451</v>
       </c>
       <c r="F43">
-        <v>-2.10905337600155</v>
+        <v>-1.533693400671694</v>
       </c>
       <c r="G43">
-        <v>-3.463338298213504</v>
+        <v>-1.907328926027418</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.075944049466323</v>
       </c>
       <c r="E44">
-        <v>-18.07998436554559</v>
+        <v>-16.43036543945345</v>
       </c>
       <c r="F44">
-        <v>-2.198451614479075</v>
+        <v>-1.460877420863409</v>
       </c>
       <c r="G44">
-        <v>-3.053115358260254</v>
+        <v>-0.7773602803812192</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.18663414496923</v>
       </c>
       <c r="E45">
-        <v>-17.96028774057485</v>
+        <v>-15.22180176781238</v>
       </c>
       <c r="F45">
-        <v>-2.045174652102069</v>
+        <v>-1.473056078419368</v>
       </c>
       <c r="G45">
-        <v>-2.402834829617833</v>
+        <v>-1.894391314059946</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.287754980375927</v>
       </c>
       <c r="E46">
-        <v>-17.04295476084106</v>
+        <v>-14.3022860636069</v>
       </c>
       <c r="F46">
-        <v>-1.923257194492843</v>
+        <v>-1.421481095553668</v>
       </c>
       <c r="G46">
-        <v>-3.577850068416895</v>
+        <v>-0.8848404518591975</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.369472253122213</v>
       </c>
       <c r="E47">
-        <v>-14.83957591919496</v>
+        <v>-14.98411575257179</v>
       </c>
       <c r="F47">
-        <v>-1.948854575606751</v>
+        <v>-1.965569373060439</v>
       </c>
       <c r="G47">
-        <v>-3.101118268579687</v>
+        <v>-1.960562498298899</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.423983551344769</v>
       </c>
       <c r="E48">
-        <v>-14.98467275487473</v>
+        <v>-14.34864858049743</v>
       </c>
       <c r="F48">
-        <v>-1.572911626989834</v>
+        <v>-1.801411804847661</v>
       </c>
       <c r="G48">
-        <v>-3.296235201573252</v>
+        <v>-1.66162354664825</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.445065448662648</v>
       </c>
       <c r="E49">
-        <v>-15.87641079951716</v>
+        <v>-13.80992319864893</v>
       </c>
       <c r="F49">
-        <v>-1.971550185708651</v>
+        <v>-1.547553644055336</v>
       </c>
       <c r="G49">
-        <v>-3.107706254202836</v>
+        <v>-1.560310921509933</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.429407491190415</v>
       </c>
       <c r="E50">
-        <v>-13.93970473523476</v>
+        <v>-12.65409813530119</v>
       </c>
       <c r="F50">
-        <v>-1.647550843451681</v>
+        <v>-1.529874626944789</v>
       </c>
       <c r="G50">
-        <v>-3.861918049505137</v>
+        <v>-1.197534720225518</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.375545474845067</v>
       </c>
       <c r="E51">
-        <v>-15.34325996917211</v>
+        <v>-12.73557443964719</v>
       </c>
       <c r="F51">
-        <v>-2.329566435361584</v>
+        <v>-1.714680081039747</v>
       </c>
       <c r="G51">
-        <v>-4.36097947900473</v>
+        <v>-2.539401454203848</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.284001553051289</v>
       </c>
       <c r="E52">
-        <v>-13.87681328821623</v>
+        <v>-12.11286850732645</v>
       </c>
       <c r="F52">
-        <v>-1.776474632553785</v>
+        <v>-1.561508321322896</v>
       </c>
       <c r="G52">
-        <v>-4.174049525129782</v>
+        <v>-1.528016549774343</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.157524074285993</v>
       </c>
       <c r="E53">
-        <v>-12.32601019344547</v>
+        <v>-10.61115407079884</v>
       </c>
       <c r="F53">
-        <v>-1.486325695844813</v>
+        <v>-1.717036786300712</v>
       </c>
       <c r="G53">
-        <v>-3.805403726604239</v>
+        <v>-1.900744250949807</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.001459580785491</v>
       </c>
       <c r="E54">
-        <v>-13.27540024067955</v>
+        <v>-11.05699592227601</v>
       </c>
       <c r="F54">
-        <v>-1.784832031280629</v>
+        <v>-1.595190568288127</v>
       </c>
       <c r="G54">
-        <v>-4.564968674043541</v>
+        <v>-1.733316720846706</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.8217228171318449</v>
       </c>
       <c r="E55">
-        <v>-12.76708356179256</v>
+        <v>-11.58571337656755</v>
       </c>
       <c r="F55">
-        <v>-1.837194791546391</v>
+        <v>-1.448533089826891</v>
       </c>
       <c r="G55">
-        <v>-4.342678783263638</v>
+        <v>-2.99653482444857</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.6244106012072124</v>
       </c>
       <c r="E56">
-        <v>-12.03584822140399</v>
+        <v>-10.48187066635386</v>
       </c>
       <c r="F56">
-        <v>-1.762781719385509</v>
+        <v>-1.835388122240886</v>
       </c>
       <c r="G56">
-        <v>-5.263109759547207</v>
+        <v>-2.28179135306546</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.4173763761214746</v>
       </c>
       <c r="E57">
-        <v>-12.40252781875308</v>
+        <v>-9.142782788389701</v>
       </c>
       <c r="F57">
-        <v>-1.859026414447172</v>
+        <v>-1.474578617705713</v>
       </c>
       <c r="G57">
-        <v>-5.376502565358323</v>
+        <v>-3.205436869067661</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.2088340267116603</v>
       </c>
       <c r="E58">
-        <v>-10.65537009100973</v>
+        <v>-10.36994037430627</v>
       </c>
       <c r="F58">
-        <v>-2.151673707242987</v>
+        <v>-1.652951798917934</v>
       </c>
       <c r="G58">
-        <v>-4.020767956115987</v>
+        <v>-2.388417403794307</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.004719604348138187</v>
       </c>
       <c r="E59">
-        <v>-11.22752466798285</v>
+        <v>-9.100043050705308</v>
       </c>
       <c r="F59">
-        <v>-2.052748415265865</v>
+        <v>-1.839056961467885</v>
       </c>
       <c r="G59">
-        <v>-4.541281720710056</v>
+        <v>-2.563078475900715</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.189805780153366</v>
       </c>
       <c r="E60">
-        <v>-9.729229229331027</v>
+        <v>-10.06322682976676</v>
       </c>
       <c r="F60">
-        <v>-1.935536912871943</v>
+        <v>-1.687773051062014</v>
       </c>
       <c r="G60">
-        <v>-5.058038016117052</v>
+        <v>-2.781922088774237</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.3687415003022237</v>
       </c>
       <c r="E61">
-        <v>-11.30195466677292</v>
+        <v>-9.17211824301139</v>
       </c>
       <c r="F61">
-        <v>-1.926155652035239</v>
+        <v>-1.508948409615268</v>
       </c>
       <c r="G61">
-        <v>-3.950216920128578</v>
+        <v>-3.233533469059455</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.5286363046746287</v>
       </c>
       <c r="E62">
-        <v>-11.36745451481986</v>
+        <v>-8.54952099406683</v>
       </c>
       <c r="F62">
-        <v>-1.169254818544857</v>
+        <v>-1.561598613369801</v>
       </c>
       <c r="G62">
-        <v>-5.355629575733218</v>
+        <v>-2.69560292438328</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.6686666187725716</v>
       </c>
       <c r="E63">
-        <v>-11.98920041065098</v>
+        <v>-7.701473666650402</v>
       </c>
       <c r="F63">
-        <v>-1.618005463296031</v>
+        <v>-1.322716506852688</v>
       </c>
       <c r="G63">
-        <v>-5.086151168836544</v>
+        <v>-3.040449211027003</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.7881652690444979</v>
       </c>
       <c r="E64">
-        <v>-10.7100831139704</v>
+        <v>-8.011456769423454</v>
       </c>
       <c r="F64">
-        <v>-1.477876348336258</v>
+        <v>-1.865264020990252</v>
       </c>
       <c r="G64">
-        <v>-4.091117048825499</v>
+        <v>-3.043902110024463</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.8866921874472153</v>
       </c>
       <c r="E65">
-        <v>-9.895320070510353</v>
+        <v>-8.827293061223322</v>
       </c>
       <c r="F65">
-        <v>-2.212878461166231</v>
+        <v>-1.413339900718954</v>
       </c>
       <c r="G65">
-        <v>-5.189787796943429</v>
+        <v>-2.826293330637089</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.9664891614124738</v>
       </c>
       <c r="E66">
-        <v>-11.34960327028163</v>
+        <v>-8.379644348617092</v>
       </c>
       <c r="F66">
-        <v>-2.485123064831094</v>
+        <v>-1.630982667028288</v>
       </c>
       <c r="G66">
-        <v>-5.675239573731076</v>
+        <v>-2.983186704834229</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.030477195820143</v>
       </c>
       <c r="E67">
-        <v>-10.41019397976045</v>
+        <v>-7.858045655465605</v>
       </c>
       <c r="F67">
-        <v>-1.989656640399043</v>
+        <v>-2.00152714528116</v>
       </c>
       <c r="G67">
-        <v>-5.016106646316643</v>
+        <v>-2.827763212856525</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.081007613663179</v>
       </c>
       <c r="E68">
-        <v>-10.77941405102784</v>
+        <v>-7.702587671256289</v>
       </c>
       <c r="F68">
-        <v>-1.764612411345696</v>
+        <v>-2.017605756569498</v>
       </c>
       <c r="G68">
-        <v>-4.968663218193348</v>
+        <v>-3.275418491222315</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.120504451915946</v>
       </c>
       <c r="E69">
-        <v>-10.44728218188327</v>
+        <v>-8.516666915141181</v>
       </c>
       <c r="F69">
-        <v>-2.175360873126039</v>
+        <v>-1.381489174081313</v>
       </c>
       <c r="G69">
-        <v>-4.772960318639332</v>
+        <v>-2.431610091445178</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.152767796823985</v>
       </c>
       <c r="E70">
-        <v>-9.763822242275621</v>
+        <v>-9.092992216675365</v>
       </c>
       <c r="F70">
-        <v>-1.925566682811848</v>
+        <v>-1.968613623265727</v>
       </c>
       <c r="G70">
-        <v>-5.495513366949583</v>
+        <v>-3.323100278624437</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.180906075771095</v>
       </c>
       <c r="E71">
-        <v>-10.87610602803962</v>
+        <v>-8.22328519808025</v>
       </c>
       <c r="F71">
-        <v>-2.319679042041769</v>
+        <v>-1.988253386018701</v>
       </c>
       <c r="G71">
-        <v>-5.427038043015298</v>
+        <v>-3.028865612185093</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.207028792650582</v>
       </c>
       <c r="E72">
-        <v>-12.5198515233438</v>
+        <v>-8.028655913704586</v>
       </c>
       <c r="F72">
-        <v>-2.173253506453317</v>
+        <v>-2.161348210140283</v>
       </c>
       <c r="G72">
-        <v>-3.881397299458209</v>
+        <v>-2.891613704672448</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.232760793520771</v>
       </c>
       <c r="E73">
-        <v>-8.31837862376732</v>
+        <v>-8.45574988279</v>
       </c>
       <c r="F73">
-        <v>-2.583842921692323</v>
+        <v>-2.544619725169766</v>
       </c>
       <c r="G73">
-        <v>-3.849364460820221</v>
+        <v>-2.614967966683252</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.258453203067486</v>
       </c>
       <c r="E74">
-        <v>-10.77476783669597</v>
+        <v>-9.154923627204266</v>
       </c>
       <c r="F74">
-        <v>-2.4129846895583</v>
+        <v>-2.546678218165723</v>
       </c>
       <c r="G74">
-        <v>-4.919759839487234</v>
+        <v>-2.491206532243138</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.283535193379456</v>
       </c>
       <c r="E75">
-        <v>-11.31683070388812</v>
+        <v>-9.393981770069184</v>
       </c>
       <c r="F75">
-        <v>-2.931807761279686</v>
+        <v>-2.259938841686674</v>
       </c>
       <c r="G75">
-        <v>-4.34594298116536</v>
+        <v>-2.29006109582256</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.305443142114505</v>
       </c>
       <c r="E76">
-        <v>-11.42227169268271</v>
+        <v>-8.901854385759615</v>
       </c>
       <c r="F76">
-        <v>-2.720250181911318</v>
+        <v>-2.724281846060743</v>
       </c>
       <c r="G76">
-        <v>-5.563627841420088</v>
+        <v>-2.680331377810622</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.321686042561139</v>
       </c>
       <c r="E77">
-        <v>-13.45141296840969</v>
+        <v>-10.00963233988598</v>
       </c>
       <c r="F77">
-        <v>-2.983014949018543</v>
+        <v>-2.729626472543605</v>
       </c>
       <c r="G77">
-        <v>-3.432292002146219</v>
+        <v>-2.580435666163114</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.328600979764275</v>
       </c>
       <c r="E78">
-        <v>-11.92276769695846</v>
+        <v>-10.75010576725019</v>
       </c>
       <c r="F78">
-        <v>-2.325500808148644</v>
+        <v>-3.02888993578558</v>
       </c>
       <c r="G78">
-        <v>-3.856763530100492</v>
+        <v>-2.598458276078906</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.323337164899137</v>
       </c>
       <c r="E79">
-        <v>-12.97127245479842</v>
+        <v>-11.39685336807766</v>
       </c>
       <c r="F79">
-        <v>-3.031794191899795</v>
+        <v>-2.937236052870231</v>
       </c>
       <c r="G79">
-        <v>-3.336504677512946</v>
+        <v>-1.671157917801351</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.30242006395293</v>
       </c>
       <c r="E80">
-        <v>-14.26271625772788</v>
+        <v>-11.51032334128786</v>
       </c>
       <c r="F80">
-        <v>-2.992770631921313</v>
+        <v>-2.990570488099477</v>
       </c>
       <c r="G80">
-        <v>-3.805066050959233</v>
+        <v>-2.422890114494737</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.262971517946547</v>
       </c>
       <c r="E81">
-        <v>-14.33879462105674</v>
+        <v>-11.80994076705735</v>
       </c>
       <c r="F81">
-        <v>-2.664200358335695</v>
+        <v>-2.78297250491649</v>
       </c>
       <c r="G81">
-        <v>-3.056396108889672</v>
+        <v>-1.471174482865057</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.20382531433744</v>
       </c>
       <c r="E82">
-        <v>-14.65182085836294</v>
+        <v>-12.17881214582615</v>
       </c>
       <c r="F82">
-        <v>-3.055790338824091</v>
+        <v>-2.728957980049546</v>
       </c>
       <c r="G82">
-        <v>-4.223260784571048</v>
+        <v>-1.056541896253498</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.125335314869129</v>
       </c>
       <c r="E83">
-        <v>-15.36675822079791</v>
+        <v>-14.72408171810334</v>
       </c>
       <c r="F83">
-        <v>-3.437740607846109</v>
+        <v>-3.167851052707405</v>
       </c>
       <c r="G83">
-        <v>-3.865596065599267</v>
+        <v>-0.9541599649059969</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.028473128899527</v>
       </c>
       <c r="E84">
-        <v>-17.30060681798147</v>
+        <v>-14.4913272110571</v>
       </c>
       <c r="F84">
-        <v>-3.533519760427399</v>
+        <v>-3.507245603145404</v>
       </c>
       <c r="G84">
-        <v>-3.190618867233883</v>
+        <v>-1.273081369431687</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.914635143638315</v>
       </c>
       <c r="E85">
-        <v>-16.34666565436968</v>
+        <v>-15.56842022530749</v>
       </c>
       <c r="F85">
-        <v>-3.326619262597569</v>
+        <v>-3.431280998839079</v>
       </c>
       <c r="G85">
-        <v>-2.992704523259634</v>
+        <v>-0.4701284121546959</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.7875432313061764</v>
       </c>
       <c r="E86">
-        <v>-18.53992335660864</v>
+        <v>-17.41601950654096</v>
       </c>
       <c r="F86">
-        <v>-3.637118701291117</v>
+        <v>-3.631199187830711</v>
       </c>
       <c r="G86">
-        <v>-3.841415840980431</v>
+        <v>-0.8063407960319992</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.6509530787643845</v>
       </c>
       <c r="E87">
-        <v>-20.81950735885581</v>
+        <v>-18.15902887934947</v>
       </c>
       <c r="F87">
-        <v>-4.088407463764468</v>
+        <v>-3.601553575219323</v>
       </c>
       <c r="G87">
-        <v>-2.862805337389711</v>
+        <v>-0.9322905010735715</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.5089852554591647</v>
       </c>
       <c r="E88">
-        <v>-21.29506052829731</v>
+        <v>-19.79791532204343</v>
       </c>
       <c r="F88">
-        <v>-3.750174284425193</v>
+        <v>-3.206124940186354</v>
       </c>
       <c r="G88">
-        <v>-3.226604497245761</v>
+        <v>-0.1035881205921294</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.3667792490431616</v>
       </c>
       <c r="E89">
-        <v>-21.08419666460414</v>
+        <v>-20.84614837144293</v>
       </c>
       <c r="F89">
-        <v>-3.6533290229965</v>
+        <v>-3.716705756249885</v>
       </c>
       <c r="G89">
-        <v>-2.472770104134936</v>
+        <v>-1.189960192031666</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.230819329175135</v>
       </c>
       <c r="E90">
-        <v>-22.98272769300188</v>
+        <v>-23.12456855587014</v>
       </c>
       <c r="F90">
-        <v>-3.449728740899423</v>
+        <v>-4.221791182963244</v>
       </c>
       <c r="G90">
-        <v>-3.636135533181303</v>
+        <v>-1.002143011952193</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.1071146390100595</v>
       </c>
       <c r="E91">
-        <v>-23.53377958109926</v>
+        <v>-23.02593386350907</v>
       </c>
       <c r="F91">
-        <v>-3.431951148067943</v>
+        <v>-3.914015416290102</v>
       </c>
       <c r="G91">
-        <v>-2.847662902093084</v>
+        <v>-1.286005739217001</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.00178270998124393</v>
       </c>
       <c r="E92">
-        <v>-25.8158814148947</v>
+        <v>-24.65346289339179</v>
       </c>
       <c r="F92">
-        <v>-4.348255549246436</v>
+        <v>-4.272919675798835</v>
       </c>
       <c r="G92">
-        <v>-3.96678951109817</v>
+        <v>-1.247451125866649</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.0780963666782432</v>
       </c>
       <c r="E93">
-        <v>-27.85475890973816</v>
+        <v>-27.29281604165234</v>
       </c>
       <c r="F93">
-        <v>-4.466621795799861</v>
+        <v>-4.64847743357345</v>
       </c>
       <c r="G93">
-        <v>-3.401209290078002</v>
+        <v>-2.262583567846609</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.1272910958936923</v>
       </c>
       <c r="E94">
-        <v>-29.83409829256578</v>
+        <v>-28.72905780097706</v>
       </c>
       <c r="F94">
-        <v>-4.582475604020594</v>
+        <v>-4.192575493033909</v>
       </c>
       <c r="G94">
-        <v>-3.901528726882517</v>
+        <v>-1.53738539365048</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.1414595109759166</v>
       </c>
       <c r="E95">
-        <v>-31.12503264216937</v>
+        <v>-31.61421651837395</v>
       </c>
       <c r="F95">
-        <v>-4.779172272182739</v>
+        <v>-4.479665268924341</v>
       </c>
       <c r="G95">
-        <v>-4.11309907120626</v>
+        <v>-1.74629074881511</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.1164375141884174</v>
       </c>
       <c r="E96">
-        <v>-33.33798920634169</v>
+        <v>-33.08332594204634</v>
       </c>
       <c r="F96">
-        <v>-4.590246518626256</v>
+        <v>-4.810421604085947</v>
       </c>
       <c r="G96">
-        <v>-4.613507892740335</v>
+        <v>-2.45367487746442</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.0521006032684846</v>
       </c>
       <c r="E97">
-        <v>-36.03385318174396</v>
+        <v>-35.21573906751824</v>
       </c>
       <c r="F97">
-        <v>-4.68475164214204</v>
+        <v>-4.926263815163042</v>
       </c>
       <c r="G97">
-        <v>-4.862010683100188</v>
+        <v>-1.908401542782142</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.05425147283182891</v>
       </c>
       <c r="E98">
-        <v>-38.17990833516397</v>
+        <v>-36.65374919594295</v>
       </c>
       <c r="F98">
-        <v>-4.891932956521419</v>
+        <v>-4.910803994324595</v>
       </c>
       <c r="G98">
-        <v>-5.461672970447153</v>
+        <v>-3.244044451146642</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.195633239920342</v>
       </c>
       <c r="E99">
-        <v>-40.42086671836272</v>
+        <v>-39.06135995109797</v>
       </c>
       <c r="F99">
-        <v>-5.179644007963952</v>
+        <v>-5.004792216581032</v>
       </c>
       <c r="G99">
-        <v>-5.258180357239231</v>
+        <v>-3.070462616886035</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.3777579848278255</v>
       </c>
       <c r="E100">
-        <v>-42.23858939233058</v>
+        <v>-41.81017310883493</v>
       </c>
       <c r="F100">
-        <v>-4.983806356798509</v>
+        <v>-5.732539487697287</v>
       </c>
       <c r="G100">
-        <v>-5.904554442145313</v>
+        <v>-4.088793045856931</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.5819725494990278</v>
       </c>
       <c r="E101">
-        <v>-43.64759464473617</v>
+        <v>-43.49788782251659</v>
       </c>
       <c r="F101">
-        <v>-5.269917002418834</v>
+        <v>-5.527643638982233</v>
       </c>
       <c r="G101">
-        <v>-5.818440531577791</v>
+        <v>-4.177422971034299</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.8277363967243166</v>
       </c>
       <c r="E102">
-        <v>-45.37925140595126</v>
+        <v>-44.84265440688637</v>
       </c>
       <c r="F102">
-        <v>-5.700885912501512</v>
+        <v>-5.512664271237409</v>
       </c>
       <c r="G102">
-        <v>-6.706732731766114</v>
+        <v>-3.597686857288207</v>
       </c>
     </row>
   </sheetData>
